--- a/assets/files/Tabel_Data_Target_vs_Realisasi.xlsx
+++ b/assets/files/Tabel_Data_Target_vs_Realisasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BBAEA1-25CF-4FEF-B3A6-394E00D3FA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6849A53-4834-43D1-B1AC-D85939C9B539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD7F4B58-4866-4660-84A1-AEA9C5919D1B}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -261,7 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -276,16 +276,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/assets/files/Tabel_Data_Target_vs_Realisasi.xlsx
+++ b/assets/files/Tabel_Data_Target_vs_Realisasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6849A53-4834-43D1-B1AC-D85939C9B539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167DCD48-3EE6-498E-A525-29411E7E280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD7F4B58-4866-4660-84A1-AEA9C5919D1B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Bulan</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Jun</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -95,7 +98,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +108,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,14 +279,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -285,7 +288,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -303,6 +312,1183 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="id-ID" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Target vs Realisasi 2025</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>_-"Rp"* #,##0_-;\-"Rp"* #,##0_-;_-"Rp"* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5F82-45B3-8614-DFADBB093698}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Realisasi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>_-"Rp"* #,##0_-;\-"Rp"* #,##0_-;_-"Rp"* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>14000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13500000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5F82-45B3-8614-DFADBB093698}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1139098256"/>
+        <c:axId val="1139109296"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1139098256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Bulan</a:t>
+                </a:r>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1139109296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1139109296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Nominal</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (Rp)</a:t>
+                </a:r>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1139098256"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32FD4331-D0A1-3612-95F4-DA19B9B82DD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,95 +1808,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5F6E05-56EB-4F60-A5E4-A1C343A60A9B}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>15000000</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="2">
         <v>14000000</v>
       </c>
+      <c r="D2" s="9">
+        <f>C2/B2</f>
+        <v>0.93333333333333335</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>15000000</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="2">
         <v>16000000</v>
       </c>
+      <c r="D3" s="9">
+        <f t="shared" ref="D3:D7" si="0">C3/B3</f>
+        <v>1.0666666666666667</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>15000000</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="2">
         <v>13500000</v>
       </c>
+      <c r="D4" s="9">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>20000000</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>19000000</v>
       </c>
+      <c r="D5" s="9">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>20000000</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="2">
         <v>18000000</v>
       </c>
+      <c r="D6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>20000000</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="7">
         <v>21000000</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" si="0"/>
+        <v>1.05</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="D2:D7">
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="90"/>
+        <cfvo type="percent" val="100"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>